--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A5F2D8-0DB4-40BC-B8B4-3A857D5FFC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C57056-9E33-455A-8A90-4C6A2BB0142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 19-12-2025'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 29-01-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C57056-9E33-455A-8A90-4C6A2BB0142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F64040-B12E-48D5-821A-FCD1E203CDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 29-01-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 02-02-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F64040-B12E-48D5-821A-FCD1E203CDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B9F8E4-4A0B-4A19-9B81-097B5B1514E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 02-02-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 20-02-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B9F8E4-4A0B-4A19-9B81-097B5B1514E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE1F9D8-A558-4CDC-9611-0DACD488A0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 20-02-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 04-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE1F9D8-A558-4CDC-9611-0DACD488A0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B197219D-2393-4455-9AE9-4A798F9A08BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 04-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 06-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B197219D-2393-4455-9AE9-4A798F9A08BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE6F074-D468-4793-85CE-50485EE979CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE6F074-D468-4793-85CE-50485EE979CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D939530-3DA6-4BE0-ADFE-F99D18BB58D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D939530-3DA6-4BE0-ADFE-F99D18BB58D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B682BA97-1744-4F04-8CC6-AC15FAF6992C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 06-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 09-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B682BA97-1744-4F04-8CC6-AC15FAF6992C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2566EA12-E26A-43F6-90CD-3847A3EAC1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2566EA12-E26A-43F6-90CD-3847A3EAC1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DA8889-3256-4C3A-8BD7-9329A6153E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 09-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 11-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DA8889-3256-4C3A-8BD7-9329A6153E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425DC6BC-D23A-48BC-8287-5C9C2101708F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425DC6BC-D23A-48BC-8287-5C9C2101708F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F78ED1-91C5-4727-BDAF-9C241C6D3A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 11-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 20-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F78ED1-91C5-4727-BDAF-9C241C6D3A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0DA49F-A28A-4C2F-BE04-C4112D35DE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 20-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 25-03-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0DA49F-A28A-4C2F-BE04-C4112D35DE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AE0766-9F00-4649-8CF0-10509B20A47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 25-03-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 08-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AE0766-9F00-4649-8CF0-10509B20A47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A38CEB-CA5D-41F0-BB91-1B33DF6313ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 08-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 10-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A38CEB-CA5D-41F0-BB91-1B33DF6313ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F94AE72-555D-4893-82DB-AAE28515DBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F94AE72-555D-4893-82DB-AAE28515DBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EB6D99-26D5-4586-B484-610DE78A9CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 10-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 14-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EB6D99-26D5-4586-B484-610DE78A9CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E691BE59-6F3C-4776-A100-B42E77704A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 14-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 24-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E691BE59-6F3C-4776-A100-B42E77704A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD800C-0390-4A3E-9996-FAF547A1C99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD800C-0390-4A3E-9996-FAF547A1C99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFF63AB-5EB7-40D0-8312-F56B2975C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 24-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 27-04-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFF63AB-5EB7-40D0-8312-F56B2975C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE7328D-7D3C-4365-9140-C5D162708A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 27-04-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 06-05-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE7328D-7D3C-4365-9140-C5D162708A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4776A3A0-97BD-4ABB-B2E4-686B9497D32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 06-05-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 01-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4776A3A0-97BD-4ABB-B2E4-686B9497D32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF524B27-CAEB-4219-B98E-E0E4807EAF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 01-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 02-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF524B27-CAEB-4219-B98E-E0E4807EAF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B07005D-F1FC-4963-BFD2-3F6630E506B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B07005D-F1FC-4963-BFD2-3F6630E506B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871125E6-43CE-4CFF-97F0-FFBA8F2C84C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 02-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 05-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C57056-9E33-455A-8A90-4C6A2BB0142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2F7E6F-379B-439F-B49E-2107C2F2F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6D985B-D792-4CAB-9418-A05EBD0969ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FD04D9-78B5-4D98-AED1-A54EEED86FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FD04D9-78B5-4D98-AED1-A54EEED86FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C59425-4EB8-473F-BB0D-850E4CD04B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C59425-4EB8-473F-BB0D-850E4CD04B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C74EF4C-40D4-4A9A-834A-5557AEE35F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 09-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 15-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C74EF4C-40D4-4A9A-834A-5557AEE35F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C9897A-7B34-47CF-931E-2B7569CB1D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 15-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 22-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C9897A-7B34-47CF-931E-2B7569CB1D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6147B290-4F9F-4186-96A5-E55573930768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 22-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 23-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6147B290-4F9F-4186-96A5-E55573930768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB852D2-0F71-42A8-BFDC-27277162EA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C9897A-7B34-47CF-931E-2B7569CB1D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17168237-3947-485E-95FA-09B8CD7148C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 22-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 23-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17168237-3947-485E-95FA-09B8CD7148C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8764C9D-5D2C-4E7A-8497-9C7332B66B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 23-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 25-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8764C9D-5D2C-4E7A-8497-9C7332B66B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D813835-9E0B-4877-A569-1A56ABFC804E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 25-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 30-06-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D813835-9E0B-4877-A569-1A56ABFC804E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FB2558-22B0-4452-A0D1-CC94E58620BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FB2558-22B0-4452-A0D1-CC94E58620BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866E6289-068D-4957-ACBC-F0C606F0E318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 30-06-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 01-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866E6289-068D-4957-ACBC-F0C606F0E318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337740CD-4167-4AEC-BCC6-336CD7EAFF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 01-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 02-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866E6289-068D-4957-ACBC-F0C606F0E318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6576497B-B737-4116-AAFF-C49D86EF7E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 01-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 03-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337740CD-4167-4AEC-BCC6-336CD7EAFF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E8CFD1-24A9-415F-92DF-3DBF880C896F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 02-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 03-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E8CFD1-24A9-415F-92DF-3DBF880C896F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93020C91-C84A-4C18-A98B-C50715462872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 03-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 09-07-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93020C91-C84A-4C18-A98B-C50715462872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F4C108-E730-435B-AE75-EA28DA36BDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 09-07-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 19-08-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F4C108-E730-435B-AE75-EA28DA36BDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE81EA4-2DC7-49EC-879E-3325DDB63F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 19-08-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 21-08-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE81EA4-2DC7-49EC-879E-3325DDB63F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DE6EC4-C004-4FC8-B3D0-26C9B7D07E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 21-08-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 27-08-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -455,9 +455,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -526,7 +526,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -549,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -572,7 +572,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -592,7 +592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -615,7 +615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -661,7 +661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -684,7 +684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -707,7 +707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -721,7 +721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -735,7 +735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DE6EC4-C004-4FC8-B3D0-26C9B7D07E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E4725E-2F83-464A-AF9D-42A3CC54D5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 27-08-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 02-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E4725E-2F83-464A-AF9D-42A3CC54D5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC87513D-34F8-47A3-840B-F87133CF6644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 02-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 06-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC87513D-34F8-47A3-840B-F87133CF6644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2D1442-AFD7-429B-B425-928286570207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2D1442-AFD7-429B-B425-928286570207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB206BE-1C6A-4768-B936-EA2DC083BC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 06-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 07-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB206BE-1C6A-4768-B936-EA2DC083BC93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE9263D-97CB-424B-B0D1-C10192C65D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 07-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 09-09-2026'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Psykologsystemer_excel.XLSX
+++ b/html/Psykologsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE9263D-97CB-424B-B0D1-C10192C65D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33016023-156E-4E75-98A9-785F0EE7F82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Psykologsystemer">'Opdateret d. 09-09-2026'!$A$1:$G$14</definedName>
+    <definedName name="Psykologsystemer">'Opdateret d. 09-09-2026'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="31">
   <si>
     <t>Standard</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Terapeut Booking _Psykolog_ (EasyPractice)</t>
+  </si>
+  <si>
+    <t>Vena _Psykolog_ (Vena)</t>
   </si>
   <si>
     <t>Xdont _Psykolog_ (CGM)</t>
@@ -454,10 +457,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,283 +482,295 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>10</v>
+      <c r="H14" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
